--- a/GURU 99 Banking Website/SRS GURU99.xlsx
+++ b/GURU 99 Banking Website/SRS GURU99.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Games\3mk\Manual Testing\GURU 99 Banking Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B376395-C5B3-4E66-9B24-57EC1E79B706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEF49EE-95BB-4251-B8BF-74F34534B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="830" xr2:uid="{46F18F15-F5BE-4E77-8066-124D7813421F}"/>
   </bookViews>
@@ -22,6 +22,11 @@
     <sheet name="Deposit" sheetId="7" r:id="rId7"/>
     <sheet name="Edit Account" sheetId="8" r:id="rId8"/>
     <sheet name="Edit Customer" sheetId="9" r:id="rId9"/>
+    <sheet name="Fund Transfer" sheetId="10" r:id="rId10"/>
+    <sheet name="Login" sheetId="11" r:id="rId11"/>
+    <sheet name="Mini Statement" sheetId="12" r:id="rId12"/>
+    <sheet name="Change Password" sheetId="13" r:id="rId13"/>
+    <sheet name="Withdraw" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="546">
   <si>
     <t>Title</t>
   </si>
@@ -1255,6 +1260,509 @@
   </si>
   <si>
     <t>System should display error if description is mandatory OR allow empty if optional (Clarification Required)</t>
+  </si>
+  <si>
+    <t>Fund Transfer</t>
+  </si>
+  <si>
+    <t>TC_FT_PAYER_001</t>
+  </si>
+  <si>
+    <t>TC_FT_PAYER_002</t>
+  </si>
+  <si>
+    <t>TC_FT_PAYER_003</t>
+  </si>
+  <si>
+    <t>User is on "Fund Transfer" page</t>
+  </si>
+  <si>
+    <t>1-Leave Payers Account number field empty
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>Verify Payers Account number is required</t>
+  </si>
+  <si>
+    <t>System should display error message "Payers account number is required"</t>
+  </si>
+  <si>
+    <t>Verify Payers Account number can't accept special characters</t>
+  </si>
+  <si>
+    <t>Verify Payers Account number can't accept characters</t>
+  </si>
+  <si>
+    <t>1-Write test data in Payers Account number field
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>TC_FT_PAYER_004</t>
+  </si>
+  <si>
+    <t>Verify Payers Account number with valid input</t>
+  </si>
+  <si>
+    <t>System accepts the valid Payers Account number without validation error</t>
+  </si>
+  <si>
+    <t>TC_FT_PAYEE_001</t>
+  </si>
+  <si>
+    <t>TC_FT_PAYEE_002</t>
+  </si>
+  <si>
+    <t>TC_FT_PAYEE_003</t>
+  </si>
+  <si>
+    <t>TC_FT_PAYEE_004</t>
+  </si>
+  <si>
+    <t>Verify Payees Account number is required</t>
+  </si>
+  <si>
+    <t>1-Leave Payees Account number field empty
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>System should display error message "Payees account number is required"</t>
+  </si>
+  <si>
+    <t>Verify Payees Account number can't accept special characters</t>
+  </si>
+  <si>
+    <t>Verify Payees Account number can't accept characters</t>
+  </si>
+  <si>
+    <t>Verify Payees Account number with valid input</t>
+  </si>
+  <si>
+    <t>1-Write test data in Payees Account number field
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>System accepts the valid Payees Account number without validation error</t>
+  </si>
+  <si>
+    <t>TC_FT_AMOUNT_001</t>
+  </si>
+  <si>
+    <t>TC_FT_AMOUNT_002</t>
+  </si>
+  <si>
+    <t>TC_FT_AMOUNT_003</t>
+  </si>
+  <si>
+    <t>TC_FT_AMOUNT_004</t>
+  </si>
+  <si>
+    <t>TC_FT_AMOUNT_005</t>
+  </si>
+  <si>
+    <t>TC_FT_AMOUNT_006</t>
+  </si>
+  <si>
+    <t>TC_FT_AMOUNT_007</t>
+  </si>
+  <si>
+    <t>TC_FT_DESC_001</t>
+  </si>
+  <si>
+    <t>TC_FT_DESC_002</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_001</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_002</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_003</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_004</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_005</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_006</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_007</t>
+  </si>
+  <si>
+    <t>User is on "Login" page</t>
+  </si>
+  <si>
+    <t>Verify User-ID is required</t>
+  </si>
+  <si>
+    <t>Verify password is required</t>
+  </si>
+  <si>
+    <t>1-Leave User-id field empty
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>System should display error message "Password is required"</t>
+  </si>
+  <si>
+    <t>Verify both fields are required</t>
+  </si>
+  <si>
+    <t>1-Leave User-id and password empty
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>Verify Login with valid input data</t>
+  </si>
+  <si>
+    <t>1-Write test data in User-id and password field
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>User should login successfully</t>
+  </si>
+  <si>
+    <t>Verify User-ID with spaces only</t>
+  </si>
+  <si>
+    <t>User-ID = " ", Password = valid</t>
+  </si>
+  <si>
+    <t>Verify Password with spaces only</t>
+  </si>
+  <si>
+    <t>Password = " ", User-ID = valid</t>
+  </si>
+  <si>
+    <t>User-ID = Valid
+Password = Valid</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_008</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_009</t>
+  </si>
+  <si>
+    <t>Verify SQL injection in User-ID</t>
+  </si>
+  <si>
+    <t>User-ID = ' OR 1=1 -- 
+ Password = valid</t>
+  </si>
+  <si>
+    <t>Verify script injection in Password</t>
+  </si>
+  <si>
+    <t>Password = &lt;script&gt;alert(1)&lt;/script&gt;, User-ID = valid</t>
+  </si>
+  <si>
+    <t>System should not allow login and handle input securely</t>
+  </si>
+  <si>
+    <t>System should sanitize input and not execute script</t>
+  </si>
+  <si>
+    <t>Verify login using Enter key</t>
+  </si>
+  <si>
+    <t>1-Write test data in User-id and password field
+2-Press on "Enter" button</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_010</t>
+  </si>
+  <si>
+    <t>Verify login using valid User-ID and invalid password</t>
+  </si>
+  <si>
+    <t>User-ID = Valid
+Password = Invalid</t>
+  </si>
+  <si>
+    <t>User-ID = Invalid
+Password = Valid</t>
+  </si>
+  <si>
+    <t>Verify login using invalid User-ID and valid password</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_011</t>
+  </si>
+  <si>
+    <t>System should display error message "User-ID is required"</t>
+  </si>
+  <si>
+    <t>System should display error messages for both fields</t>
+  </si>
+  <si>
+    <t>System should display error message "Incorrect password"</t>
+  </si>
+  <si>
+    <t>System should display error message "Account does not exist"</t>
+  </si>
+  <si>
+    <t>System should display error message "User-ID cannot be empty or contain only spaces"</t>
+  </si>
+  <si>
+    <t>System should display error message "Password cannot be empty or contain only spaces"</t>
+  </si>
+  <si>
+    <t>1-Leave Password field empty
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>Mini Statement</t>
+  </si>
+  <si>
+    <t>User is on "Mini Statement  Form" page</t>
+  </si>
+  <si>
+    <t>TC_MS_AccNO_001</t>
+  </si>
+  <si>
+    <t>TC_MS_AccNO_002</t>
+  </si>
+  <si>
+    <t>TC_MS_AccNO_003</t>
+  </si>
+  <si>
+    <t>TC_MS_AccNO_004</t>
+  </si>
+  <si>
+    <t>Withdraw</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AccNO_001</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AccNO_002</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AccNO_003</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AccNO_004</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AMOUNT_001</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AMOUNT_002</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AMOUNT_003</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AMOUNT_004</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AMOUNT_005</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AMOUNT_006</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_AMOUNT_007</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_DESC_001</t>
+  </si>
+  <si>
+    <t>TC_Withdraw_DESC_002</t>
+  </si>
+  <si>
+    <t>User is on "Withdraw" page</t>
+  </si>
+  <si>
+    <t>Change Password</t>
+  </si>
+  <si>
+    <t>TC_CP_OLDP_001</t>
+  </si>
+  <si>
+    <t>TC_CP_NEWP_001</t>
+  </si>
+  <si>
+    <t>TC_CP_NEWP_003</t>
+  </si>
+  <si>
+    <t>TC_CP_NEWP_002</t>
+  </si>
+  <si>
+    <t>Verify Old Password is required</t>
+  </si>
+  <si>
+    <t>Verify New Password is required</t>
+  </si>
+  <si>
+    <t>User is on "Change Password" page</t>
+  </si>
+  <si>
+    <t>1-Leave Old Password field empty
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>1-Leave New Password field empty
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>System should display error message "Old Password is required"</t>
+  </si>
+  <si>
+    <t>System should display error message "New Password is required"</t>
+  </si>
+  <si>
+    <t>Verify Confirm Password is required</t>
+  </si>
+  <si>
+    <t>1-Leave Confirm Password field empty
+2-Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>System should display error message "Confirm Password is required"</t>
+  </si>
+  <si>
+    <t>Verify New Password must contain at least one numeric value</t>
+  </si>
+  <si>
+    <t>TC_CP_CONFP_002</t>
+  </si>
+  <si>
+    <t>TC_CP_NEWP_004</t>
+  </si>
+  <si>
+    <t>TC_CP_CONFP_001</t>
+  </si>
+  <si>
+    <t>TC_CP_CONFP_003</t>
+  </si>
+  <si>
+    <t>Verify Password Mismatch</t>
+  </si>
+  <si>
+    <t>Verify Password Match</t>
+  </si>
+  <si>
+    <t>TC_CP_NEWP_005</t>
+  </si>
+  <si>
+    <t>Verify New Password with no numeric value</t>
+  </si>
+  <si>
+    <t>abcd@a</t>
+  </si>
+  <si>
+    <t>1abc@b</t>
+  </si>
+  <si>
+    <t>System should accept valid data</t>
+  </si>
+  <si>
+    <t>TC_CP_NEWP_006</t>
+  </si>
+  <si>
+    <t>1abcb</t>
+  </si>
+  <si>
+    <t>TC_CP_NEWP_007</t>
+  </si>
+  <si>
+    <t>123abc</t>
+  </si>
+  <si>
+    <t>P@ss0rd</t>
+  </si>
+  <si>
+    <t>System should display error message indicating weak password</t>
+  </si>
+  <si>
+    <t>New Password = 1@bc
+Confirm Password =1b@c</t>
+  </si>
+  <si>
+    <t>New Password = 1@bc
+Confirm Password =1@bc</t>
+  </si>
+  <si>
+    <t>System should display error message "Passwords do not match"</t>
+  </si>
+  <si>
+    <t>1. Enter valid Old Password
+2. Enter New Password
+3. Enter different value in Confirm Password
+4. Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>1. Enter valid Old Password
+2. Enter New Password
+3. Enter same value in Confirm Password
+4. Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>Verify successful password change</t>
+  </si>
+  <si>
+    <t>Old Password = Valid
+New Password = 1@bc
+Confirm Password =1@bc</t>
+  </si>
+  <si>
+    <t>TC_CP_CONFP_004</t>
+  </si>
+  <si>
+    <t>TC_CP_OLDP_002</t>
+  </si>
+  <si>
+    <t>Verify Old Password incorrect</t>
+  </si>
+  <si>
+    <t>Old Password = Invalid</t>
+  </si>
+  <si>
+    <t>System should display error message "Incorrect Old Password"</t>
+  </si>
+  <si>
+    <t>1. Enter invalid Old Password
+2. Enter valid New Password
+3. Enter matching Confirm Password
+4. Click on "Submit" button</t>
+  </si>
+  <si>
+    <t>1. Enter valid Old Password
+2. Enter New Password
+3. Click on "Submit" button
+4.Enter same value in Confirm Password</t>
+  </si>
+  <si>
+    <t>System should display error message "Password must contain at least one numeric value"</t>
+  </si>
+  <si>
+    <t>Verify New Password with valid special character</t>
+  </si>
+  <si>
+    <t>Verify New Password without special character</t>
+  </si>
+  <si>
+    <t>System should display error message "Password must contain at least one special character"</t>
+  </si>
+  <si>
+    <t>Verify Password difficulty (Weak Password)</t>
+  </si>
+  <si>
+    <t>Verify Password difficulty (Strong Password)</t>
+  </si>
+  <si>
+    <t>P@ss1word</t>
+  </si>
+  <si>
+    <t>System should change the password successfully</t>
   </si>
 </sst>
 </file>
@@ -2117,6 +2625,1630 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4A3C5BE-BA5E-434E-9E9B-1AAB2F310AA9}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="25.21875" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="31.8" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="80.400000000000006" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="80.400000000000006" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="80.400000000000006" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E5" s="7">
+        <v>12345678</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="80.400000000000006" thickBot="1">
+      <c r="A7" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="80.400000000000006" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="80.400000000000006" thickBot="1">
+      <c r="A9" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E9" s="7">
+        <v>12345678</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="54" thickBot="1">
+      <c r="A10" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="54" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="54" thickBot="1">
+      <c r="A12" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="54" thickBot="1">
+      <c r="A13" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="54" thickBot="1">
+      <c r="A14" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="54" thickBot="1">
+      <c r="A15" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="54" thickBot="1">
+      <c r="A16" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="67.2" thickBot="1">
+      <c r="A17" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="67.2" thickBot="1">
+      <c r="A18" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E18" r:id="rId1" xr:uid="{6607D997-D05D-4BFA-99E2-6B519D40BD62}"/>
+    <hyperlink ref="E11" r:id="rId2" xr:uid="{7DAEFC6C-8743-4FD9-893C-686DDFCACF62}"/>
+    <hyperlink ref="E3" r:id="rId3" xr:uid="{EA6AFCE8-3F34-44D0-88E0-E3D6B4952680}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72B8AB4-4F40-465C-8033-0D12B8FC96F6}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="36.21875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="31.8" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="54" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A7" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A9" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A10" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="67.2" thickBot="1">
+      <c r="A12" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25A854F7-EB23-4C5D-BD13-F8BD5CEA7168}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="18.88671875" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="24.77734375" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="47.4" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="152.4" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="133.19999999999999" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E3" s="7">
+        <v>123456789</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="138.6" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="152.4" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9FFE1F8-4C9F-40F5-B1BD-2338626ED77E}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="5" max="5" width="27.21875" customWidth="1"/>
+    <col min="6" max="6" width="20.5546875" customWidth="1"/>
+    <col min="7" max="7" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="31.8" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="54" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="106.8" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="54" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A7" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A9" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A10" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="54" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A12" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A13" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="93.6" thickBot="1">
+      <c r="A14" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" thickBot="1">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="3"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E7" r:id="rId1" xr:uid="{E6E33DFC-EBB6-4751-B322-1208C0A3CA03}"/>
+    <hyperlink ref="E10" r:id="rId2" xr:uid="{AB8B7201-6DFC-4C4D-BFE8-FFB27E9FB91D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F57721-27CB-445E-A541-3C9506F57CA4}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="5" max="5" width="27.21875" customWidth="1"/>
+    <col min="6" max="6" width="20.5546875" customWidth="1"/>
+    <col min="7" max="7" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="47.4" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="54" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="54" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E3" s="7">
+        <v>123456789</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="55.8" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="55.8" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="54" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="55.8" thickBot="1">
+      <c r="A7" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="55.8" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="54" thickBot="1">
+      <c r="A9" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="54" thickBot="1">
+      <c r="A10" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="54" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="54" thickBot="1">
+      <c r="A12" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="69.599999999999994" thickBot="1">
+      <c r="A13" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="54" thickBot="1">
+      <c r="A14" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E14" r:id="rId1" xr:uid="{5012E4FB-748C-4293-BBB9-DE2C90BD2965}"/>
+    <hyperlink ref="E7" r:id="rId2" xr:uid="{DFB616A8-E893-4257-BCA6-D51BED3713C7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAB69E2-5685-49D7-A509-9C66B9DF65A6}">
   <dimension ref="A1:I43"/>
@@ -3391,7 +5523,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="55.8" thickBot="1">
+    <row r="4" spans="1:9" ht="42" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>202</v>
       </c>
@@ -3414,7 +5546,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="55.8" thickBot="1">
+    <row r="5" spans="1:9" ht="42" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>202</v>
       </c>
@@ -3460,7 +5592,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="69.599999999999994" thickBot="1">
+    <row r="7" spans="1:9" ht="42" thickBot="1">
       <c r="A7" s="4" t="s">
         <v>202</v>
       </c>
@@ -3483,7 +5615,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="55.8" thickBot="1">
+    <row r="8" spans="1:9" ht="42" thickBot="1">
       <c r="A8" s="4" t="s">
         <v>202</v>
       </c>
@@ -3529,7 +5661,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="55.8" thickBot="1">
+    <row r="10" spans="1:9" ht="42" thickBot="1">
       <c r="A10" s="4" t="s">
         <v>202</v>
       </c>
@@ -3552,7 +5684,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="55.8" thickBot="1">
+    <row r="11" spans="1:9" ht="42" thickBot="1">
       <c r="A11" s="4" t="s">
         <v>202</v>
       </c>
@@ -3621,7 +5753,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="55.8" thickBot="1">
+    <row r="14" spans="1:9" ht="42" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>202</v>
       </c>
@@ -3644,7 +5776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="69.599999999999994" thickBot="1">
+    <row r="15" spans="1:9" ht="55.8" thickBot="1">
       <c r="A15" s="4" t="s">
         <v>202</v>
       </c>
@@ -3690,7 +5822,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="55.8" thickBot="1">
+    <row r="17" spans="1:7" ht="42" thickBot="1">
       <c r="A17" s="4" t="s">
         <v>202</v>
       </c>
@@ -3713,7 +5845,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="55.8" thickBot="1">
+    <row r="18" spans="1:7" ht="42" thickBot="1">
       <c r="A18" s="4" t="s">
         <v>202</v>
       </c>

--- a/GURU 99 Banking Website/SRS GURU99.xlsx
+++ b/GURU 99 Banking Website/SRS GURU99.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Games\3mk\Manual Testing\GURU 99 Banking Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEF49EE-95BB-4251-B8BF-74F34534B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724C8C44-9B16-444D-97F3-6542EFEF8E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="830" xr2:uid="{46F18F15-F5BE-4E77-8066-124D7813421F}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="588">
   <si>
     <t>Title</t>
   </si>
@@ -1763,13 +1763,140 @@
   </si>
   <si>
     <t>System should change the password successfully</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Error message "Customer name must not be blank"</t>
+  </si>
+  <si>
+    <t>Error message "Special characters are not allowed"</t>
+  </si>
+  <si>
+    <t>Error message "Numbers are not allowed"</t>
+  </si>
+  <si>
+    <t>Valid Customer Name without validation error</t>
+  </si>
+  <si>
+    <t>Valid Address without validation error</t>
+  </si>
+  <si>
+    <t>Error message "City is required"</t>
+  </si>
+  <si>
+    <t>Valid City without validation error</t>
+  </si>
+  <si>
+    <t>Error message "State is required"</t>
+  </si>
+  <si>
+    <t>Valid State input without validation error</t>
+  </si>
+  <si>
+    <t>Error message "PIN is required"</t>
+  </si>
+  <si>
+    <t>Error message "Characters are not allowed"</t>
+  </si>
+  <si>
+    <t>Valid PIN input without validation error</t>
+  </si>
+  <si>
+    <t>Error message "PIN must have 6 Digits"</t>
+  </si>
+  <si>
+    <t>Error message "Telephone number is required"</t>
+  </si>
+  <si>
+    <t>Valid Telephone number without validation error</t>
+  </si>
+  <si>
+    <t>Error message "Email is required"</t>
+  </si>
+  <si>
+    <t>Error message "Email is not valid"</t>
+  </si>
+  <si>
+    <t>Valid Email without validation error</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>No error message is shown</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>System can't accept more than 6 digits</t>
+  </si>
+  <si>
+    <t>" 123"</t>
+  </si>
+  <si>
+    <t>Error message "
+Account Number must not be blank"</t>
+  </si>
+  <si>
+    <t>TC_DA_ACCNO_005</t>
+  </si>
+  <si>
+    <t>Error message "Account Number must not be blank"</t>
+  </si>
+  <si>
+    <t>Error message "characters are not allowed"</t>
+  </si>
+  <si>
+    <t>An error message "Customer ID is required" must be shown</t>
+  </si>
+  <si>
+    <t>An error message "Special characters are not allowed" must be shown</t>
+  </si>
+  <si>
+    <t>An error message "Account Number must not be blank" is shown</t>
+  </si>
+  <si>
+    <t>An error message "Characters are not allowed" must be shown</t>
+  </si>
+  <si>
+    <t>An error message "Special characters are not allowed" is shown</t>
+  </si>
+  <si>
+    <t>An error message "Customer ID is required" is shown</t>
+  </si>
+  <si>
+    <t>An error message "Characters are not allowed" is shown</t>
+  </si>
+  <si>
+    <t>Cannot be executed</t>
+  </si>
+  <si>
+    <t>Error message "User-ID is required"</t>
+  </si>
+  <si>
+    <t>Error message "Password is required"</t>
+  </si>
+  <si>
+    <t>Error message "User-ID is required", Error message "Password is required"</t>
+  </si>
+  <si>
+    <t>User logged in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forbidden message </t>
+  </si>
+  <si>
+    <t>Error message "Account number is required"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1816,8 +1943,22 @@
       <color theme="1"/>
       <name val="Droid Sans"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1833,6 +1974,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1876,7 +2035,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1917,12 +2076,83 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2317,8 +2547,12 @@
       <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A3" s="4" t="s">
@@ -2342,8 +2576,12 @@
       <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A4" s="4" t="s">
@@ -2367,8 +2605,12 @@
       <c r="G4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="55.8" thickBot="1">
       <c r="A5" s="4" t="s">
@@ -2392,8 +2634,12 @@
       <c r="G5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="83.4" thickBot="1">
       <c r="A6" s="4" t="s">
@@ -2408,8 +2654,8 @@
       <c r="D6" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="4">
-        <v>123</v>
+      <c r="E6" s="4" t="s">
+        <v>569</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>26</v>
@@ -2417,8 +2663,12 @@
       <c r="G6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="55.8" thickBot="1">
       <c r="A7" s="4" t="s">
@@ -2442,8 +2692,12 @@
       <c r="G7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="55.8" thickBot="1">
       <c r="A8" s="4" t="s">
@@ -2467,8 +2721,12 @@
       <c r="G8" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="55.8" thickBot="1">
       <c r="A9" s="4" t="s">
@@ -2492,8 +2750,12 @@
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="55.8" thickBot="1">
       <c r="A10" s="4" t="s">
@@ -2517,8 +2779,12 @@
       <c r="G10" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="55.8" thickBot="1">
       <c r="A11" s="4" t="s">
@@ -2542,8 +2808,12 @@
       <c r="G11" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="55.8" thickBot="1">
       <c r="A12" s="4" t="s">
@@ -2567,8 +2837,12 @@
       <c r="G12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="55.8" thickBot="1">
       <c r="A13" s="4" t="s">
@@ -2592,8 +2866,12 @@
       <c r="G13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="55.8" thickBot="1">
       <c r="A14" s="4" t="s">
@@ -2617,8 +2895,12 @@
       <c r="G14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>567</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3135,6 +3417,12 @@
       <c r="G2" s="3" t="s">
         <v>463</v>
       </c>
+      <c r="H2" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="67.2" thickBot="1">
       <c r="A3" s="4" t="s">
@@ -3158,8 +3446,14 @@
       <c r="G3" s="3" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="67.2" thickBot="1">
+      <c r="H3" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>424</v>
       </c>
@@ -3180,6 +3474,12 @@
       </c>
       <c r="G4" s="3" t="s">
         <v>464</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="67.2" thickBot="1">
@@ -3204,6 +3504,12 @@
       <c r="G5" s="3" t="s">
         <v>441</v>
       </c>
+      <c r="H5" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="67.2" thickBot="1">
       <c r="A6" s="4" t="s">
@@ -3227,6 +3533,12 @@
       <c r="G6" s="3" t="s">
         <v>467</v>
       </c>
+      <c r="H6" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="67.2" thickBot="1">
       <c r="A7" s="4" t="s">
@@ -3250,6 +3562,12 @@
       <c r="G7" s="3" t="s">
         <v>468</v>
       </c>
+      <c r="H7" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="67.2" thickBot="1">
       <c r="A8" s="4" t="s">
@@ -3273,6 +3591,12 @@
       <c r="G8" s="3" t="s">
         <v>453</v>
       </c>
+      <c r="H8" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="I8" s="26" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="67.2" thickBot="1">
       <c r="A9" s="4" t="s">
@@ -3296,6 +3620,12 @@
       <c r="G9" s="3" t="s">
         <v>454</v>
       </c>
+      <c r="H9" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="67.2" thickBot="1">
       <c r="A10" s="4" t="s">
@@ -3319,6 +3649,12 @@
       <c r="G10" s="3" t="s">
         <v>441</v>
       </c>
+      <c r="H10" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="67.2" thickBot="1">
       <c r="A11" s="4" t="s">
@@ -3342,6 +3678,12 @@
       <c r="G11" s="3" t="s">
         <v>465</v>
       </c>
+      <c r="H11" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="67.2" thickBot="1">
       <c r="A12" s="4" t="s">
@@ -3364,6 +3706,12 @@
       </c>
       <c r="G12" s="3" t="s">
         <v>466</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -3378,14 +3726,14 @@
   <cols>
     <col min="1" max="1" width="18.88671875" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="24.77734375" customWidth="1"/>
     <col min="7" max="7" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="47.4" thickBot="1">
+    <row r="1" spans="1:9" ht="31.8" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3414,7 +3762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="152.4" thickBot="1">
+    <row r="2" spans="1:9" ht="124.8" thickBot="1">
       <c r="A2" s="4" t="s">
         <v>470</v>
       </c>
@@ -3436,8 +3784,14 @@
       <c r="G2" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="133.19999999999999" thickBot="1">
+      <c r="H2" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>470</v>
       </c>
@@ -3459,8 +3813,14 @@
       <c r="G3" s="3" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="138.6" thickBot="1">
+      <c r="H3" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="111" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>470</v>
       </c>
@@ -3482,8 +3842,14 @@
       <c r="G4" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="152.4" thickBot="1">
+      <c r="H4" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="138.6" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>470</v>
       </c>
@@ -3505,8 +3871,22 @@
       <c r="G5" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="H5" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>546</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3912,7 +4292,7 @@
     <col min="7" max="7" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="47.4" thickBot="1">
+    <row r="1" spans="1:9" ht="31.8" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -4261,6 +4641,8 @@
     <col min="5" max="5" width="15.44140625" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="23.21875" customWidth="1"/>
+    <col min="8" max="8" width="40.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.8" thickBot="1">
@@ -4314,6 +4696,12 @@
       <c r="G2" s="3" t="s">
         <v>68</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="83.4" thickBot="1">
       <c r="A3" s="4" t="s">
@@ -4337,6 +4725,12 @@
       <c r="G3" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="83.4" thickBot="1">
       <c r="A4" s="4" t="s">
@@ -4360,6 +4754,12 @@
       <c r="G4" s="3" t="s">
         <v>103</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="83.4" thickBot="1">
       <c r="A5" s="4" t="s">
@@ -4383,6 +4783,12 @@
       <c r="G5" s="3" t="s">
         <v>272</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="83.4" thickBot="1">
       <c r="A6" s="4" t="s">
@@ -4406,6 +4812,12 @@
       <c r="G6" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="83.4" thickBot="1">
       <c r="A7" s="4" t="s">
@@ -4429,6 +4841,12 @@
       <c r="G7" s="3" t="s">
         <v>76</v>
       </c>
+      <c r="H7" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A8" s="4" t="s">
@@ -4452,6 +4870,12 @@
       <c r="G8" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="H8" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A9" s="4" t="s">
@@ -4475,6 +4899,12 @@
       <c r="G9" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="H9" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A10" s="4" t="s">
@@ -4498,6 +4928,12 @@
       <c r="G10" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="H10" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A11" s="4" t="s">
@@ -4521,6 +4957,12 @@
       <c r="G11" s="3" t="s">
         <v>273</v>
       </c>
+      <c r="H11" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="55.8" thickBot="1">
       <c r="A12" s="4" t="s">
@@ -4544,6 +4986,12 @@
       <c r="G12" s="3" t="s">
         <v>98</v>
       </c>
+      <c r="H12" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="55.8" thickBot="1">
       <c r="A13" s="4" t="s">
@@ -4567,6 +5015,12 @@
       <c r="G13" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="H13" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="55.8" thickBot="1">
       <c r="A14" s="4" t="s">
@@ -4590,6 +5044,12 @@
       <c r="G14" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="H14" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="55.8" thickBot="1">
       <c r="A15" s="4" t="s">
@@ -4613,6 +5073,12 @@
       <c r="G15" s="3" t="s">
         <v>103</v>
       </c>
+      <c r="H15" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="54" thickBot="1">
       <c r="A16" s="4" t="s">
@@ -4636,8 +5102,14 @@
       <c r="G16" s="3" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="54" thickBot="1">
+      <c r="H16" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="54" thickBot="1">
       <c r="A17" s="8" t="s">
         <v>59</v>
       </c>
@@ -4659,8 +5131,14 @@
       <c r="G17" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H17" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="55.8" thickBot="1">
       <c r="A18" s="4" t="s">
         <v>59</v>
       </c>
@@ -4682,8 +5160,14 @@
       <c r="G18" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H18" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="55.8" thickBot="1">
       <c r="A19" s="4" t="s">
         <v>59</v>
       </c>
@@ -4705,8 +5189,14 @@
       <c r="G19" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H19" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="55.8" thickBot="1">
       <c r="A20" s="4" t="s">
         <v>59</v>
       </c>
@@ -4728,8 +5218,14 @@
       <c r="G20" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="54" thickBot="1">
+      <c r="H20" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="54" thickBot="1">
       <c r="A21" s="4" t="s">
         <v>59</v>
       </c>
@@ -4751,8 +5247,14 @@
       <c r="G21" s="3" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="54" thickBot="1">
+      <c r="H21" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="54" thickBot="1">
       <c r="A22" s="4" t="s">
         <v>59</v>
       </c>
@@ -4774,8 +5276,14 @@
       <c r="G22" s="3" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="54" thickBot="1">
+      <c r="H22" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="54" thickBot="1">
       <c r="A23" s="4" t="s">
         <v>59</v>
       </c>
@@ -4797,8 +5305,14 @@
       <c r="G23" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H23" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="55.8" thickBot="1">
       <c r="A24" s="4" t="s">
         <v>59</v>
       </c>
@@ -4820,8 +5334,14 @@
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H24" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="55.8" thickBot="1">
       <c r="A25" s="4" t="s">
         <v>59</v>
       </c>
@@ -4843,8 +5363,14 @@
       <c r="G25" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H25" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="55.8" thickBot="1">
       <c r="A26" s="4" t="s">
         <v>59</v>
       </c>
@@ -4866,8 +5392,14 @@
       <c r="G26" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="54" thickBot="1">
+      <c r="H26" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="54" thickBot="1">
       <c r="A27" s="4" t="s">
         <v>59</v>
       </c>
@@ -4889,8 +5421,14 @@
       <c r="G27" s="3" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="54" thickBot="1">
+      <c r="H27" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="54" thickBot="1">
       <c r="A28" s="4" t="s">
         <v>59</v>
       </c>
@@ -4912,8 +5450,14 @@
       <c r="G28" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="54" thickBot="1">
+      <c r="H28" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="54" thickBot="1">
       <c r="A29" s="4" t="s">
         <v>59</v>
       </c>
@@ -4935,8 +5479,14 @@
       <c r="G29" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="67.2" thickBot="1">
+      <c r="H29" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="67.2" thickBot="1">
       <c r="A30" s="4" t="s">
         <v>59</v>
       </c>
@@ -4958,8 +5508,14 @@
       <c r="G30" s="3" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="83.4" thickBot="1">
+      <c r="H30" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="83.4" thickBot="1">
       <c r="A31" s="4" t="s">
         <v>59</v>
       </c>
@@ -4981,8 +5537,14 @@
       <c r="G31" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="H31" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A32" s="4" t="s">
         <v>59</v>
       </c>
@@ -5004,8 +5566,14 @@
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="67.2" thickBot="1">
+      <c r="H32" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="I32" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="67.2" thickBot="1">
       <c r="A33" s="4" t="s">
         <v>59</v>
       </c>
@@ -5027,8 +5595,14 @@
       <c r="G33" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="67.2" thickBot="1">
+      <c r="H33" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="67.2" thickBot="1">
       <c r="A34" s="4" t="s">
         <v>59</v>
       </c>
@@ -5050,8 +5624,14 @@
       <c r="G34" s="3" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="54" thickBot="1">
+      <c r="H34" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="54" thickBot="1">
       <c r="A35" s="4" t="s">
         <v>59</v>
       </c>
@@ -5073,8 +5653,14 @@
       <c r="G35" s="3" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="54" thickBot="1">
+      <c r="H35" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="I35" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="54" thickBot="1">
       <c r="A36" s="4" t="s">
         <v>59</v>
       </c>
@@ -5096,8 +5682,14 @@
       <c r="G36" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H36" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="55.8" thickBot="1">
       <c r="A37" s="4" t="s">
         <v>59</v>
       </c>
@@ -5119,8 +5711,14 @@
       <c r="G37" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H37" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="55.8" thickBot="1">
       <c r="A38" s="4" t="s">
         <v>59</v>
       </c>
@@ -5142,8 +5740,14 @@
       <c r="G38" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="54" thickBot="1">
+      <c r="H38" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="54" thickBot="1">
       <c r="A39" s="4" t="s">
         <v>59</v>
       </c>
@@ -5165,8 +5769,14 @@
       <c r="G39" s="3" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="54" thickBot="1">
+      <c r="H39" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="54" thickBot="1">
       <c r="A40" s="4" t="s">
         <v>59</v>
       </c>
@@ -5188,8 +5798,14 @@
       <c r="G40" s="3" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="55.8" thickBot="1">
+      <c r="H40" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="55.8" thickBot="1">
       <c r="A41" s="4" t="s">
         <v>59</v>
       </c>
@@ -5211,8 +5827,14 @@
       <c r="G41" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="54" thickBot="1">
+      <c r="H41" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="54" thickBot="1">
       <c r="A42" s="4" t="s">
         <v>59</v>
       </c>
@@ -5234,8 +5856,14 @@
       <c r="G42" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="54" thickBot="1">
+      <c r="H42" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="54" thickBot="1">
       <c r="A43" s="4" t="s">
         <v>59</v>
       </c>
@@ -5256,6 +5884,12 @@
       </c>
       <c r="G43" s="3" t="s">
         <v>176</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -5444,11 +6078,13 @@
     <col min="3" max="3" width="22.5546875" customWidth="1"/>
     <col min="4" max="4" width="23.109375" customWidth="1"/>
     <col min="5" max="5" width="18.44140625" customWidth="1"/>
-    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
     <col min="7" max="7" width="30.33203125" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.8" thickBot="1">
+    <row r="1" spans="1:9" ht="16.2" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -5499,8 +6135,14 @@
       <c r="G2" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="42" thickBot="1">
+      <c r="H2" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>202</v>
       </c>
@@ -5522,8 +6164,14 @@
       <c r="G3" s="3" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="42" thickBot="1">
+      <c r="H3" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>202</v>
       </c>
@@ -5545,8 +6193,14 @@
       <c r="G4" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="42" thickBot="1">
+      <c r="H4" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>202</v>
       </c>
@@ -5568,8 +6222,14 @@
       <c r="G5" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="42" thickBot="1">
+      <c r="H5" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="67.2" thickBot="1">
       <c r="A6" s="4" t="s">
         <v>202</v>
       </c>
@@ -5591,8 +6251,14 @@
       <c r="G6" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="42" thickBot="1">
+      <c r="H6" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="67.2" thickBot="1">
       <c r="A7" s="4" t="s">
         <v>202</v>
       </c>
@@ -5614,8 +6280,14 @@
       <c r="G7" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="42" thickBot="1">
+      <c r="H7" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="67.2" thickBot="1">
       <c r="A8" s="4" t="s">
         <v>202</v>
       </c>
@@ -5637,8 +6309,14 @@
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="55.8" thickBot="1">
+      <c r="H8" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="67.2" thickBot="1">
       <c r="A9" s="4" t="s">
         <v>202</v>
       </c>
@@ -5660,8 +6338,14 @@
       <c r="G9" s="3" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="42" thickBot="1">
+      <c r="H9" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="67.2" thickBot="1">
       <c r="A10" s="4" t="s">
         <v>202</v>
       </c>
@@ -5683,8 +6367,14 @@
       <c r="G10" s="10" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="42" thickBot="1">
+      <c r="H10" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="67.2" thickBot="1">
       <c r="A11" s="4" t="s">
         <v>202</v>
       </c>
@@ -5706,8 +6396,14 @@
       <c r="G11" s="3" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="42" thickBot="1">
+      <c r="H11" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="67.2" thickBot="1">
       <c r="A12" s="4" t="s">
         <v>202</v>
       </c>
@@ -5729,8 +6425,14 @@
       <c r="G12" s="3" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="42" thickBot="1">
+      <c r="H12" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A13" s="4" t="s">
         <v>202</v>
       </c>
@@ -5752,8 +6454,14 @@
       <c r="G13" s="3" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="42" thickBot="1">
+      <c r="H13" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>202</v>
       </c>
@@ -5775,8 +6483,14 @@
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="55.8" thickBot="1">
+      <c r="H14" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A15" s="4" t="s">
         <v>202</v>
       </c>
@@ -5798,8 +6512,14 @@
       <c r="G15" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="42" thickBot="1">
+      <c r="H15" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A16" s="4" t="s">
         <v>202</v>
       </c>
@@ -5821,8 +6541,14 @@
       <c r="G16" s="3" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="42" thickBot="1">
+      <c r="H16" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A17" s="4" t="s">
         <v>202</v>
       </c>
@@ -5844,8 +6570,14 @@
       <c r="G17" s="3" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="42" thickBot="1">
+      <c r="H17" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A18" s="4" t="s">
         <v>202</v>
       </c>
@@ -5867,8 +6599,14 @@
       <c r="G18" s="3" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="42" thickBot="1">
+      <c r="H18" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="80.400000000000006" thickBot="1">
       <c r="A19" s="4" t="s">
         <v>202</v>
       </c>
@@ -5890,8 +6628,14 @@
       <c r="G19" s="3" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="83.4" thickBot="1">
+      <c r="H19" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="83.4" thickBot="1">
       <c r="A20" s="4" t="s">
         <v>202</v>
       </c>
@@ -5912,6 +6656,10 @@
       </c>
       <c r="G20" s="3" t="s">
         <v>271</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="19" t="s">
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -5925,7 +6673,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AFA872-773B-464B-92F2-ABB29761A799}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -5966,7 +6714,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="53.4" thickBot="1">
+    <row r="2" spans="1:9" ht="111" thickBot="1">
       <c r="A2" s="4" t="s">
         <v>283</v>
       </c>
@@ -5988,8 +6736,14 @@
       <c r="G2" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="67.2" thickBot="1">
+      <c r="H2" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="111" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>283</v>
       </c>
@@ -6011,8 +6765,14 @@
       <c r="G3" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="67.2" thickBot="1">
+      <c r="H3" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="97.2" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>283</v>
       </c>
@@ -6033,6 +6793,12 @@
       </c>
       <c r="G4" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="67.2" thickBot="1">
@@ -6056,6 +6822,23 @@
       </c>
       <c r="G5" s="3" t="s">
         <v>279</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>571</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -6068,7 +6851,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C39FEA-3FE0-487D-A95C-F1086E0F584B}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.109375" customWidth="1"/>
@@ -6078,6 +6861,7 @@
     <col min="5" max="5" width="17.44140625" customWidth="1"/>
     <col min="6" max="6" width="18.33203125" customWidth="1"/>
     <col min="7" max="7" width="30.5546875" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.8" thickBot="1">
@@ -6109,7 +6893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="54" thickBot="1">
+    <row r="2" spans="1:9" ht="55.8" thickBot="1">
       <c r="A2" s="4" t="s">
         <v>290</v>
       </c>
@@ -6130,6 +6914,12 @@
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="54" thickBot="1">
@@ -6154,6 +6944,12 @@
       <c r="G3" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="H3" s="25" t="s">
+        <v>575</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="54" thickBot="1">
       <c r="A4" s="4" t="s">
@@ -6177,6 +6973,12 @@
       <c r="G4" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="54" thickBot="1">
       <c r="A5" s="4" t="s">
@@ -6200,6 +7002,12 @@
       <c r="G5" s="3" t="s">
         <v>301</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="54" thickBot="1">
       <c r="A6" s="4" t="s">
@@ -6223,6 +7031,15 @@
       <c r="G6" s="3" t="s">
         <v>300</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1">
+      <c r="H7" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6627,7 +7444,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="53.4" thickBot="1">
+    <row r="2" spans="1:9" ht="124.8" thickBot="1">
       <c r="A2" s="8" t="s">
         <v>334</v>
       </c>
@@ -6649,8 +7466,14 @@
       <c r="G2" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="67.2" thickBot="1">
+      <c r="H2" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="124.8" thickBot="1">
       <c r="A3" s="8" t="s">
         <v>334</v>
       </c>
@@ -6672,8 +7495,14 @@
       <c r="G3" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="67.2" thickBot="1">
+      <c r="H3" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="124.8" thickBot="1">
       <c r="A4" s="8" t="s">
         <v>334</v>
       </c>
@@ -6694,6 +7523,12 @@
       </c>
       <c r="G4" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="67.2" thickBot="1">
@@ -6717,6 +7552,12 @@
       </c>
       <c r="G5" s="3" t="s">
         <v>279</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -6770,7 +7611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="54" thickBot="1">
+    <row r="2" spans="1:9" ht="111" thickBot="1">
       <c r="A2" s="4" t="s">
         <v>340</v>
       </c>
@@ -6792,8 +7633,14 @@
       <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="67.2" thickBot="1">
+      <c r="H2" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="124.8" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>340</v>
       </c>
@@ -6815,8 +7662,14 @@
       <c r="G3" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="67.2" thickBot="1">
+      <c r="H3" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="111" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>340</v>
       </c>
@@ -6837,6 +7690,12 @@
       </c>
       <c r="G4" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="67.2" thickBot="1">
@@ -6861,6 +7720,12 @@
       <c r="G5" s="3" t="s">
         <v>301</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="67.2" thickBot="1">
       <c r="A6" s="4" t="s">
@@ -6884,6 +7749,12 @@
       <c r="G6" s="3" t="s">
         <v>300</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A7" s="4" t="s">
@@ -6907,6 +7778,12 @@
       <c r="G7" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="H7" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="55.8" thickBot="1">
       <c r="A8" s="4" t="s">
@@ -6930,6 +7807,12 @@
       <c r="G8" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="H8" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="55.8" thickBot="1">
       <c r="A9" s="4" t="s">
@@ -6953,6 +7836,12 @@
       <c r="G9" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="H9" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="55.8" thickBot="1">
       <c r="A10" s="4" t="s">
@@ -6976,6 +7865,12 @@
       <c r="G10" s="3" t="s">
         <v>273</v>
       </c>
+      <c r="H10" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="55.8" thickBot="1">
       <c r="A11" s="4" t="s">
@@ -6999,6 +7894,12 @@
       <c r="G11" s="3" t="s">
         <v>98</v>
       </c>
+      <c r="H11" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="55.8" thickBot="1">
       <c r="A12" s="4" t="s">
@@ -7022,6 +7923,12 @@
       <c r="G12" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="H12" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="55.8" thickBot="1">
       <c r="A13" s="4" t="s">
@@ -7045,8 +7952,14 @@
       <c r="G13" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="54" thickBot="1">
+      <c r="H13" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="55.8" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>349</v>
       </c>
@@ -7068,8 +7981,14 @@
       <c r="G14" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="54" thickBot="1">
+      <c r="H14" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="55.8" thickBot="1">
       <c r="A15" s="4" t="s">
         <v>349</v>
       </c>
@@ -7091,8 +8010,14 @@
       <c r="G15" s="3" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="54" thickBot="1">
+      <c r="H15" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="55.8" thickBot="1">
       <c r="A16" s="4" t="s">
         <v>349</v>
       </c>
@@ -7114,8 +8039,14 @@
       <c r="G16" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="54" thickBot="1">
+      <c r="H16" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="55.8" thickBot="1">
       <c r="A17" s="4" t="s">
         <v>349</v>
       </c>
@@ -7137,8 +8068,14 @@
       <c r="G17" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="54" thickBot="1">
+      <c r="H17" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="55.8" thickBot="1">
       <c r="A18" s="4" t="s">
         <v>349</v>
       </c>
@@ -7160,8 +8097,14 @@
       <c r="G18" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="54" thickBot="1">
+      <c r="H18" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="55.8" thickBot="1">
       <c r="A19" s="4" t="s">
         <v>349</v>
       </c>
@@ -7183,8 +8126,14 @@
       <c r="G19" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="54" thickBot="1">
+      <c r="H19" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="55.8" thickBot="1">
       <c r="A20" s="4" t="s">
         <v>349</v>
       </c>
@@ -7206,8 +8155,14 @@
       <c r="G20" s="3" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="54" thickBot="1">
+      <c r="H20" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="55.8" thickBot="1">
       <c r="A21" s="4" t="s">
         <v>349</v>
       </c>
@@ -7229,8 +8184,14 @@
       <c r="G21" s="3" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="54" thickBot="1">
+      <c r="H21" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="55.8" thickBot="1">
       <c r="A22" s="4" t="s">
         <v>349</v>
       </c>
@@ -7252,8 +8213,14 @@
       <c r="G22" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="54" thickBot="1">
+      <c r="H22" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="55.8" thickBot="1">
       <c r="A23" s="4" t="s">
         <v>349</v>
       </c>
@@ -7275,8 +8242,14 @@
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="54" thickBot="1">
+      <c r="H23" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="55.8" thickBot="1">
       <c r="A24" s="4" t="s">
         <v>349</v>
       </c>
@@ -7298,8 +8271,14 @@
       <c r="G24" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="54" thickBot="1">
+      <c r="H24" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="55.8" thickBot="1">
       <c r="A25" s="4" t="s">
         <v>349</v>
       </c>
@@ -7321,8 +8300,14 @@
       <c r="G25" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="54" thickBot="1">
+      <c r="H25" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="55.8" thickBot="1">
       <c r="A26" s="4" t="s">
         <v>349</v>
       </c>
@@ -7344,8 +8329,14 @@
       <c r="G26" s="3" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="54" thickBot="1">
+      <c r="H26" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="55.8" thickBot="1">
       <c r="A27" s="4" t="s">
         <v>349</v>
       </c>
@@ -7367,8 +8358,14 @@
       <c r="G27" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="54" thickBot="1">
+      <c r="H27" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="55.8" thickBot="1">
       <c r="A28" s="4" t="s">
         <v>349</v>
       </c>
@@ -7390,8 +8387,14 @@
       <c r="G28" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="67.2" thickBot="1">
+      <c r="H28" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="67.2" thickBot="1">
       <c r="A29" s="4" t="s">
         <v>349</v>
       </c>
@@ -7413,8 +8416,14 @@
       <c r="G29" s="3" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="67.2" thickBot="1">
+      <c r="H29" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="67.2" thickBot="1">
       <c r="A30" s="4" t="s">
         <v>349</v>
       </c>
@@ -7436,8 +8445,14 @@
       <c r="G30" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="67.2" thickBot="1">
+      <c r="H30" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="67.2" thickBot="1">
       <c r="A31" s="4" t="s">
         <v>349</v>
       </c>
@@ -7459,8 +8474,14 @@
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="67.2" thickBot="1">
+      <c r="H31" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="67.2" thickBot="1">
       <c r="A32" s="4" t="s">
         <v>349</v>
       </c>
@@ -7482,8 +8503,14 @@
       <c r="G32" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="67.2" thickBot="1">
+      <c r="H32" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I32" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="67.2" thickBot="1">
       <c r="A33" s="4" t="s">
         <v>349</v>
       </c>
@@ -7505,8 +8532,14 @@
       <c r="G33" s="3" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="54" thickBot="1">
+      <c r="H33" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="55.8" thickBot="1">
       <c r="A34" s="4" t="s">
         <v>349</v>
       </c>
@@ -7528,8 +8561,14 @@
       <c r="G34" s="3" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="54" thickBot="1">
+      <c r="H34" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I34" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="55.8" thickBot="1">
       <c r="A35" s="4" t="s">
         <v>349</v>
       </c>
@@ -7551,8 +8590,14 @@
       <c r="G35" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="54" thickBot="1">
+      <c r="H35" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I35" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="55.8" thickBot="1">
       <c r="A36" s="4" t="s">
         <v>349</v>
       </c>
@@ -7574,8 +8619,14 @@
       <c r="G36" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="54" thickBot="1">
+      <c r="H36" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="55.8" thickBot="1">
       <c r="A37" s="4" t="s">
         <v>349</v>
       </c>
@@ -7597,8 +8648,14 @@
       <c r="G37" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="54" thickBot="1">
+      <c r="H37" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="55.8" thickBot="1">
       <c r="A38" s="4" t="s">
         <v>349</v>
       </c>
@@ -7620,8 +8677,14 @@
       <c r="G38" s="3" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="54" thickBot="1">
+      <c r="H38" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="55.8" thickBot="1">
       <c r="A39" s="4" t="s">
         <v>349</v>
       </c>
@@ -7643,8 +8706,14 @@
       <c r="G39" s="3" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="54" thickBot="1">
+      <c r="H39" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I39" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="55.8" thickBot="1">
       <c r="A40" s="4" t="s">
         <v>349</v>
       </c>
@@ -7666,8 +8735,14 @@
       <c r="G40" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="54" thickBot="1">
+      <c r="H40" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="55.8" thickBot="1">
       <c r="A41" s="4" t="s">
         <v>349</v>
       </c>
@@ -7689,8 +8764,14 @@
       <c r="G41" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="54" thickBot="1">
+      <c r="H41" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="55.8" thickBot="1">
       <c r="A42" s="4" t="s">
         <v>349</v>
       </c>
@@ -7711,6 +8792,12 @@
       </c>
       <c r="G42" s="3" t="s">
         <v>176</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
